--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/61.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/61.xlsx
@@ -426,13 +426,13 @@
         <v>-4.78430468848558</v>
       </c>
       <c r="E2">
-        <v>-21.77569251911477</v>
+        <v>-19.10016055796963</v>
       </c>
       <c r="F2">
-        <v>-3.072423956272305</v>
+        <v>-3.531456297227026</v>
       </c>
       <c r="G2">
-        <v>-13.43250098502672</v>
+        <v>-11.54454625545233</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.34617665470184</v>
       </c>
       <c r="E3">
-        <v>-20.37481433925011</v>
+        <v>-20.78712024031114</v>
       </c>
       <c r="F3">
-        <v>-3.146171021041337</v>
+        <v>-3.442929501257245</v>
       </c>
       <c r="G3">
-        <v>-12.55124284292414</v>
+        <v>-11.52411717902687</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.047876203017988</v>
       </c>
       <c r="E4">
-        <v>-22.10666192959036</v>
+        <v>-20.42484392286899</v>
       </c>
       <c r="F4">
-        <v>-3.965056930548399</v>
+        <v>-3.387155524026755</v>
       </c>
       <c r="G4">
-        <v>-12.50425205102869</v>
+        <v>-11.61366571850206</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.937212887926247</v>
       </c>
       <c r="E5">
-        <v>-21.15576343071424</v>
+        <v>-20.77220190523235</v>
       </c>
       <c r="F5">
-        <v>-3.197835467586539</v>
+        <v>-3.519198944767802</v>
       </c>
       <c r="G5">
-        <v>-11.6130939654366</v>
+        <v>-11.37983829531588</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.979507902543185</v>
       </c>
       <c r="E6">
-        <v>-22.44037245954033</v>
+        <v>-21.81008526209568</v>
       </c>
       <c r="F6">
-        <v>-3.498305033766989</v>
+        <v>-3.569739296747405</v>
       </c>
       <c r="G6">
-        <v>-11.31394701795307</v>
+        <v>-11.16379004279519</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.154089623258082</v>
       </c>
       <c r="E7">
-        <v>-22.15789179128212</v>
+        <v>-21.8161614102639</v>
       </c>
       <c r="F7">
-        <v>-4.071797040603532</v>
+        <v>-3.284043663195884</v>
       </c>
       <c r="G7">
-        <v>-11.54824698591023</v>
+        <v>-10.9428335904432</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.416213902828143</v>
       </c>
       <c r="E8">
-        <v>-23.64125274805788</v>
+        <v>-22.44326309462241</v>
       </c>
       <c r="F8">
-        <v>-3.26883649441529</v>
+        <v>-3.176649142892539</v>
       </c>
       <c r="G8">
-        <v>-11.65253578934685</v>
+        <v>-11.26774467092414</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.725859298869741</v>
       </c>
       <c r="E9">
-        <v>-23.91709658461902</v>
+        <v>-22.96719070324954</v>
       </c>
       <c r="F9">
-        <v>-2.612815899972639</v>
+        <v>-3.173308337157048</v>
       </c>
       <c r="G9">
-        <v>-10.613301492036</v>
+        <v>-10.96693337376377</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.035416397343121</v>
       </c>
       <c r="E10">
-        <v>-24.90980546190219</v>
+        <v>-23.79083065392158</v>
       </c>
       <c r="F10">
-        <v>-3.153473079697014</v>
+        <v>-3.269795743867732</v>
       </c>
       <c r="G10">
-        <v>-10.23631127845153</v>
+        <v>-10.32823037401545</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.301168541317171</v>
       </c>
       <c r="E11">
-        <v>-25.18620998199218</v>
+        <v>-23.96244549907482</v>
       </c>
       <c r="F11">
-        <v>-3.077875442150128</v>
+        <v>-2.924614218753775</v>
       </c>
       <c r="G11">
-        <v>-10.16330050058875</v>
+        <v>-10.46876544998278</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.488690721547271</v>
       </c>
       <c r="E12">
-        <v>-24.89406894419241</v>
+        <v>-24.513530956555</v>
       </c>
       <c r="F12">
-        <v>-2.588386516896678</v>
+        <v>-2.765521288841713</v>
       </c>
       <c r="G12">
-        <v>-10.41868092574686</v>
+        <v>-10.23750047261279</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.572201235736721</v>
       </c>
       <c r="E13">
-        <v>-26.05453433330806</v>
+        <v>-25.43784059652956</v>
       </c>
       <c r="F13">
-        <v>-2.804971458032637</v>
+        <v>-2.616285931022965</v>
       </c>
       <c r="G13">
-        <v>-10.07235390738503</v>
+        <v>-10.33529113276212</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.545084752875804</v>
       </c>
       <c r="E14">
-        <v>-26.75792220328102</v>
+        <v>-25.88589318746339</v>
       </c>
       <c r="F14">
-        <v>-2.702362416215265</v>
+        <v>-2.788306362623116</v>
       </c>
       <c r="G14">
-        <v>-9.90860278514122</v>
+        <v>-9.373317905508376</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.416361225665206</v>
       </c>
       <c r="E15">
-        <v>-25.99278023411918</v>
+        <v>-25.92264910768812</v>
       </c>
       <c r="F15">
-        <v>-2.516571204910975</v>
+        <v>-2.603061873804674</v>
       </c>
       <c r="G15">
-        <v>-9.829626455887748</v>
+        <v>-8.909808921546714</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.207237516119264</v>
       </c>
       <c r="E16">
-        <v>-28.43408353617797</v>
+        <v>-26.88549224233445</v>
       </c>
       <c r="F16">
-        <v>-2.346160291174463</v>
+        <v>-2.157285896396954</v>
       </c>
       <c r="G16">
-        <v>-9.014374463909984</v>
+        <v>-8.464977204389877</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.951213632816907</v>
       </c>
       <c r="E17">
-        <v>-28.19315990043599</v>
+        <v>-28.08575162575894</v>
       </c>
       <c r="F17">
-        <v>-1.82066554839093</v>
+        <v>-2.22328772594981</v>
       </c>
       <c r="G17">
-        <v>-8.459826205311611</v>
+        <v>-8.488120149817801</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.682367453238816</v>
       </c>
       <c r="E18">
-        <v>-28.9046776815773</v>
+        <v>-28.65212713073147</v>
       </c>
       <c r="F18">
-        <v>-2.395737251864611</v>
+        <v>-1.992914609394254</v>
       </c>
       <c r="G18">
-        <v>-7.713713256968004</v>
+        <v>-8.064331034065336</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.432643323939757</v>
       </c>
       <c r="E19">
-        <v>-29.25872233417364</v>
+        <v>-28.89712091357178</v>
       </c>
       <c r="F19">
-        <v>-1.705327813062141</v>
+        <v>-1.889241943831687</v>
       </c>
       <c r="G19">
-        <v>-7.991653126137925</v>
+        <v>-7.888573097446999</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.231126410003069</v>
       </c>
       <c r="E20">
-        <v>-31.41621386374461</v>
+        <v>-30.06904293612696</v>
       </c>
       <c r="F20">
-        <v>-1.383425897069058</v>
+        <v>-1.873529470935386</v>
       </c>
       <c r="G20">
-        <v>-7.869475500763006</v>
+        <v>-7.585302478881802</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.094224909167914</v>
       </c>
       <c r="E21">
-        <v>-30.84046871402326</v>
+        <v>-30.04027571788554</v>
       </c>
       <c r="F21">
-        <v>-0.9365945795901716</v>
+        <v>-1.648071058180639</v>
       </c>
       <c r="G21">
-        <v>-7.35031980121406</v>
+        <v>-7.261922600103556</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.033354383724992</v>
       </c>
       <c r="E22">
-        <v>-31.18539083794461</v>
+        <v>-30.94693420972958</v>
       </c>
       <c r="F22">
-        <v>-1.319496642758007</v>
+        <v>-1.384226099980163</v>
       </c>
       <c r="G22">
-        <v>-7.140308895560316</v>
+        <v>-7.080068574864968</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.049543144849507</v>
       </c>
       <c r="E23">
-        <v>-31.0539354696968</v>
+        <v>-31.20600322574974</v>
       </c>
       <c r="F23">
-        <v>-0.8231993658209472</v>
+        <v>-1.020146200938738</v>
       </c>
       <c r="G23">
-        <v>-6.798369233483845</v>
+        <v>-6.683958573267487</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.135562543644285</v>
       </c>
       <c r="E24">
-        <v>-32.67566066175922</v>
+        <v>-32.02897035618716</v>
       </c>
       <c r="F24">
-        <v>-0.915095960385316</v>
+        <v>-0.9673245251318249</v>
       </c>
       <c r="G24">
-        <v>-6.941169130383968</v>
+        <v>-6.559867272107281</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.283171247679493</v>
       </c>
       <c r="E25">
-        <v>-32.64802104039249</v>
+        <v>-31.99810784283236</v>
       </c>
       <c r="F25">
-        <v>-0.8437710419020702</v>
+        <v>-0.8929727521587496</v>
       </c>
       <c r="G25">
-        <v>-7.265128594461443</v>
+        <v>-6.541208280514595</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.473602183154717</v>
       </c>
       <c r="E26">
-        <v>-32.45457899312161</v>
+        <v>-32.21961936884209</v>
       </c>
       <c r="F26">
-        <v>-1.019820652549438</v>
+        <v>-0.8262195933715543</v>
       </c>
       <c r="G26">
-        <v>-6.851367348683445</v>
+        <v>-6.989091958098443</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.690216302381994</v>
       </c>
       <c r="E27">
-        <v>-33.09406763025643</v>
+        <v>-32.08249279053022</v>
       </c>
       <c r="F27">
-        <v>-1.028072848616127</v>
+        <v>-0.9943334443001027</v>
       </c>
       <c r="G27">
-        <v>-7.111843947283408</v>
+        <v>-6.784025802700269</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.915139033495267</v>
       </c>
       <c r="E28">
-        <v>-32.33432691242253</v>
+        <v>-32.04913004395788</v>
       </c>
       <c r="F28">
-        <v>-0.7073546696416448</v>
+        <v>-0.9420485505702035</v>
       </c>
       <c r="G28">
-        <v>-6.9391327496029</v>
+        <v>-6.381362832179093</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.129774358390248</v>
       </c>
       <c r="E29">
-        <v>-33.16428805073097</v>
+        <v>-32.85058769294402</v>
       </c>
       <c r="F29">
-        <v>-0.8775974247953879</v>
+        <v>-0.8614931341175628</v>
       </c>
       <c r="G29">
-        <v>-7.241900799834307</v>
+        <v>-6.846858592774591</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.321800579475695</v>
       </c>
       <c r="E30">
-        <v>-31.76320013369439</v>
+        <v>-32.48036835884314</v>
       </c>
       <c r="F30">
-        <v>-0.7486347024253526</v>
+        <v>-0.9438419659972644</v>
       </c>
       <c r="G30">
-        <v>-7.256181572747697</v>
+        <v>-6.89807095867387</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.478050533183157</v>
       </c>
       <c r="E31">
-        <v>-33.08814515090722</v>
+        <v>-31.80104834849756</v>
       </c>
       <c r="F31">
-        <v>-0.9073399563929042</v>
+        <v>-0.834066717778274</v>
       </c>
       <c r="G31">
-        <v>-6.836376453241272</v>
+        <v>-7.061064964986254</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.589984068601654</v>
       </c>
       <c r="E32">
-        <v>-30.36450861959225</v>
+        <v>-31.38475744117035</v>
       </c>
       <c r="F32">
-        <v>-1.099870764886371</v>
+        <v>-0.8790992548966635</v>
       </c>
       <c r="G32">
-        <v>-7.06952116671687</v>
+        <v>-7.103708867137499</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.652504535821127</v>
       </c>
       <c r="E33">
-        <v>-30.51077641603006</v>
+        <v>-31.09644774081774</v>
       </c>
       <c r="F33">
-        <v>-1.113130441902983</v>
+        <v>-0.9508077074874055</v>
       </c>
       <c r="G33">
-        <v>-7.062208471117162</v>
+        <v>-6.830523163867996</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.659743410533057</v>
       </c>
       <c r="E34">
-        <v>-31.28402130048664</v>
+        <v>-30.76357200634406</v>
       </c>
       <c r="F34">
-        <v>-0.4702817175322459</v>
+        <v>-0.8822139163311896</v>
       </c>
       <c r="G34">
-        <v>-6.812665670864781</v>
+        <v>-7.114245832307232</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.610879039884305</v>
       </c>
       <c r="E35">
-        <v>-30.99571160013403</v>
+        <v>-30.09736783736229</v>
       </c>
       <c r="F35">
-        <v>-1.236875278002784</v>
+        <v>-1.018118357536685</v>
       </c>
       <c r="G35">
-        <v>-7.499902412561895</v>
+        <v>-7.071638480580264</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.503367657427481</v>
       </c>
       <c r="E36">
-        <v>-30.44620851616861</v>
+        <v>-30.31737174766111</v>
       </c>
       <c r="F36">
-        <v>-0.888248572860584</v>
+        <v>-1.100949299244816</v>
       </c>
       <c r="G36">
-        <v>-6.784931731073384</v>
+        <v>-7.40798592774257</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.337699620405883</v>
       </c>
       <c r="E37">
-        <v>-30.17970109866569</v>
+        <v>-29.65519827027008</v>
       </c>
       <c r="F37">
-        <v>-0.8724333824063358</v>
+        <v>-1.161278468823301</v>
       </c>
       <c r="G37">
-        <v>-7.823470264950703</v>
+        <v>-7.328157190380099</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.116022360214776</v>
       </c>
       <c r="E38">
-        <v>-30.4577897459479</v>
+        <v>-29.24219878291781</v>
       </c>
       <c r="F38">
-        <v>-0.9829317953679704</v>
+        <v>-1.193227771181875</v>
       </c>
       <c r="G38">
-        <v>-7.04210573776559</v>
+        <v>-7.44196476859591</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.838633289994632</v>
       </c>
       <c r="E39">
-        <v>-28.97493132774244</v>
+        <v>-28.59458646443163</v>
       </c>
       <c r="F39">
-        <v>-1.364315461086474</v>
+        <v>-1.321737376582579</v>
       </c>
       <c r="G39">
-        <v>-6.821409054500419</v>
+        <v>-7.135883683478379</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.513905489714307</v>
       </c>
       <c r="E40">
-        <v>-27.99660917448848</v>
+        <v>-28.71355104962002</v>
       </c>
       <c r="F40">
-        <v>-1.560598773914622</v>
+        <v>-1.222148562315814</v>
       </c>
       <c r="G40">
-        <v>-7.594951790890557</v>
+        <v>-7.500273138293834</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.146552806692675</v>
       </c>
       <c r="E41">
-        <v>-26.61890591381636</v>
+        <v>-28.25263803981886</v>
       </c>
       <c r="F41">
-        <v>-0.9699057179589481</v>
+        <v>-1.113581073770106</v>
       </c>
       <c r="G41">
-        <v>-7.640214269866688</v>
+        <v>-7.515527718939708</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.747028287100874</v>
       </c>
       <c r="E42">
-        <v>-27.12090871985971</v>
+        <v>-28.10767019852572</v>
       </c>
       <c r="F42">
-        <v>-0.8393367911948845</v>
+        <v>-1.302358549561488</v>
       </c>
       <c r="G42">
-        <v>-8.382150026864513</v>
+        <v>-7.294267114842858</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.327881687587518</v>
       </c>
       <c r="E43">
-        <v>-26.75383959654871</v>
+        <v>-26.63970104291977</v>
       </c>
       <c r="F43">
-        <v>-0.5940837109828404</v>
+        <v>-1.17377107762492</v>
       </c>
       <c r="G43">
-        <v>-7.684116550910849</v>
+        <v>-7.599123760747156</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.898192067118715</v>
       </c>
       <c r="E44">
-        <v>-27.01991092686253</v>
+        <v>-25.98274607555839</v>
       </c>
       <c r="F44">
-        <v>-0.8898572623568207</v>
+        <v>-1.199592946304987</v>
       </c>
       <c r="G44">
-        <v>-7.959166325818407</v>
+        <v>-7.424464947601678</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.475739679005058</v>
       </c>
       <c r="E45">
-        <v>-27.22625492511398</v>
+        <v>-26.28686912803029</v>
       </c>
       <c r="F45">
-        <v>-1.138467715652411</v>
+        <v>-0.9495253947478719</v>
       </c>
       <c r="G45">
-        <v>-7.918805519812091</v>
+        <v>-7.11867104438917</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.07227528278605</v>
       </c>
       <c r="E46">
-        <v>-25.93147052854206</v>
+        <v>-25.94852776745313</v>
       </c>
       <c r="F46">
-        <v>-0.4740474757453724</v>
+        <v>-1.280686801569447</v>
       </c>
       <c r="G46">
-        <v>-9.144299473859032</v>
+        <v>-7.510637794320553</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.700908098313553</v>
       </c>
       <c r="E47">
-        <v>-25.20122384093143</v>
+        <v>-25.07150243841174</v>
       </c>
       <c r="F47">
-        <v>-0.7538028866514187</v>
+        <v>-1.223297507903497</v>
       </c>
       <c r="G47">
-        <v>-8.484230140377042</v>
+        <v>-7.672922983476451</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.376090862875807</v>
       </c>
       <c r="E48">
-        <v>-24.54503721766515</v>
+        <v>-24.96852356361261</v>
       </c>
       <c r="F48">
-        <v>-0.7363508422092386</v>
+        <v>-1.059685005441761</v>
       </c>
       <c r="G48">
-        <v>-7.674710038149068</v>
+        <v>-7.629674693952364</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.104827914474456</v>
       </c>
       <c r="E49">
-        <v>-23.16457207146201</v>
+        <v>-23.63105661425543</v>
       </c>
       <c r="F49">
-        <v>-0.6706563369628211</v>
+        <v>-1.399965080633353</v>
       </c>
       <c r="G49">
-        <v>-8.347485865556006</v>
+        <v>-7.883255010714902</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.8956401034204853</v>
       </c>
       <c r="E50">
-        <v>-23.95762777393802</v>
+        <v>-23.58897627711227</v>
       </c>
       <c r="F50">
-        <v>-1.035707082600327</v>
+        <v>-1.005518889340104</v>
       </c>
       <c r="G50">
-        <v>-8.234213489981373</v>
+        <v>-7.721606843239236</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.7507838803707808</v>
       </c>
       <c r="E51">
-        <v>-22.6337044467111</v>
+        <v>-22.61659321605281</v>
       </c>
       <c r="F51">
-        <v>-0.8470323243668918</v>
+        <v>-1.297598750465002</v>
       </c>
       <c r="G51">
-        <v>-8.13973194860128</v>
+        <v>-7.709663992107188</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.666619200698892</v>
       </c>
       <c r="E52">
-        <v>-22.88548042364486</v>
+        <v>-22.89076330845004</v>
       </c>
       <c r="F52">
-        <v>-0.8544039658844046</v>
+        <v>-0.9894295092755296</v>
       </c>
       <c r="G52">
-        <v>-8.585994353794048</v>
+        <v>-7.922850868556021</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.6399924560203324</v>
       </c>
       <c r="E53">
-        <v>-22.35955512037049</v>
+        <v>-22.38729441880902</v>
       </c>
       <c r="F53">
-        <v>-1.321676077394772</v>
+        <v>-1.428030996607603</v>
       </c>
       <c r="G53">
-        <v>-8.975790269597921</v>
+        <v>-7.819332234773788</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.6629098635416107</v>
       </c>
       <c r="E54">
-        <v>-22.36723025489878</v>
+        <v>-21.81275577697754</v>
       </c>
       <c r="F54">
-        <v>-1.363506146133939</v>
+        <v>-1.219918597267478</v>
       </c>
       <c r="G54">
-        <v>-8.563286097340544</v>
+        <v>-8.059539012368349</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.7275019595288386</v>
       </c>
       <c r="E55">
-        <v>-21.82442630080031</v>
+        <v>-21.08058615252352</v>
       </c>
       <c r="F55">
-        <v>-1.092765029305157</v>
+        <v>-1.289007752130568</v>
       </c>
       <c r="G55">
-        <v>-8.380973886426217</v>
+        <v>-7.72876811565266</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.8267495454091786</v>
       </c>
       <c r="E56">
-        <v>-21.19987884140657</v>
+        <v>-21.28748252788118</v>
       </c>
       <c r="F56">
-        <v>-1.205611863853728</v>
+        <v>-1.606967467653728</v>
       </c>
       <c r="G56">
-        <v>-9.083762833652592</v>
+        <v>-8.540597421471473</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.9517222522147991</v>
       </c>
       <c r="E57">
-        <v>-21.90658512722807</v>
+        <v>-20.70825906367529</v>
       </c>
       <c r="F57">
-        <v>-1.672139273068979</v>
+        <v>-1.440231191716035</v>
       </c>
       <c r="G57">
-        <v>-9.120394191010503</v>
+        <v>-8.479840173347085</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.095068414324678</v>
       </c>
       <c r="E58">
-        <v>-21.02629122087404</v>
+        <v>-20.37110967474836</v>
       </c>
       <c r="F58">
-        <v>-1.245173862644029</v>
+        <v>-1.54392705156588</v>
       </c>
       <c r="G58">
-        <v>-9.04337200408348</v>
+        <v>-8.828857564010065</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.250799872147477</v>
       </c>
       <c r="E59">
-        <v>-21.25026560119939</v>
+        <v>-20.11231477067564</v>
       </c>
       <c r="F59">
-        <v>-1.562343315664918</v>
+        <v>-1.36172515621792</v>
       </c>
       <c r="G59">
-        <v>-9.474618711760458</v>
+        <v>-8.570117110563192</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.411756939168277</v>
       </c>
       <c r="E60">
-        <v>-21.10750726833106</v>
+        <v>-20.31976767635083</v>
       </c>
       <c r="F60">
-        <v>-1.203573251675438</v>
+        <v>-1.385037900034906</v>
       </c>
       <c r="G60">
-        <v>-8.608466337862055</v>
+        <v>-9.062002277485664</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.573516326816735</v>
       </c>
       <c r="E61">
-        <v>-19.8869532177678</v>
+        <v>-19.01217062284181</v>
       </c>
       <c r="F61">
-        <v>-1.304014455999684</v>
+        <v>-1.492878082000957</v>
       </c>
       <c r="G61">
-        <v>-9.739430451753966</v>
+        <v>-9.116057744244664</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.733626622534966</v>
       </c>
       <c r="E62">
-        <v>-19.68519851803028</v>
+        <v>-19.05263120756829</v>
       </c>
       <c r="F62">
-        <v>-1.447045341971463</v>
+        <v>-1.673970793396568</v>
       </c>
       <c r="G62">
-        <v>-9.51968407951996</v>
+        <v>-9.009249572277628</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.888423790938561</v>
       </c>
       <c r="E63">
-        <v>-21.99572550189287</v>
+        <v>-18.83499878093595</v>
       </c>
       <c r="F63">
-        <v>-1.643825675241291</v>
+        <v>-1.714322226321738</v>
       </c>
       <c r="G63">
-        <v>-9.985681103076953</v>
+        <v>-9.554589734703145</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.040114247396222</v>
       </c>
       <c r="E64">
-        <v>-19.67294654462203</v>
+        <v>-19.33567255935536</v>
       </c>
       <c r="F64">
-        <v>-1.901305458318656</v>
+        <v>-1.872595900872431</v>
       </c>
       <c r="G64">
-        <v>-9.223410256458946</v>
+        <v>-9.421031873655563</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.188904377250709</v>
       </c>
       <c r="E65">
-        <v>-20.40090065958136</v>
+        <v>-18.09062286839826</v>
       </c>
       <c r="F65">
-        <v>-1.97772814979873</v>
+        <v>-2.118912604829669</v>
       </c>
       <c r="G65">
-        <v>-10.00918563663075</v>
+        <v>-9.447684965186237</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.335628881628274</v>
       </c>
       <c r="E66">
-        <v>-19.10441759957758</v>
+        <v>-18.16026391589298</v>
       </c>
       <c r="F66">
-        <v>-2.027884967670837</v>
+        <v>-2.024267487222812</v>
       </c>
       <c r="G66">
-        <v>-9.883608821798196</v>
+        <v>-9.233763164135006</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.483485370675473</v>
       </c>
       <c r="E67">
-        <v>-18.29574997573154</v>
+        <v>-18.21613291463457</v>
       </c>
       <c r="F67">
-        <v>-2.261340439332211</v>
+        <v>-2.087521622100582</v>
       </c>
       <c r="G67">
-        <v>-9.280485049337569</v>
+        <v>-9.806923420923427</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.630929366734121</v>
       </c>
       <c r="E68">
-        <v>-18.45184842337522</v>
+        <v>-18.18566910956696</v>
       </c>
       <c r="F68">
-        <v>-2.107370961806464</v>
+        <v>-2.174954144731264</v>
       </c>
       <c r="G68">
-        <v>-9.70923719055774</v>
+        <v>-9.605854315494245</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.780011979111523</v>
       </c>
       <c r="E69">
-        <v>-19.20722619271238</v>
+        <v>-17.96988901518549</v>
       </c>
       <c r="F69">
-        <v>-2.500230001155949</v>
+        <v>-2.375886255423924</v>
       </c>
       <c r="G69">
-        <v>-8.893686268324295</v>
+        <v>-9.386976015836785</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.929100929263125</v>
       </c>
       <c r="E70">
-        <v>-19.10325885361795</v>
+        <v>-18.35723826939562</v>
       </c>
       <c r="F70">
-        <v>-2.196348389643367</v>
+        <v>-2.296047376774704</v>
       </c>
       <c r="G70">
-        <v>-9.687022364831957</v>
+        <v>-9.318188117350132</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.075136972843341</v>
       </c>
       <c r="E71">
-        <v>-18.85647503669664</v>
+        <v>-17.74914583327085</v>
       </c>
       <c r="F71">
-        <v>-1.786901293052822</v>
+        <v>-2.226586284947758</v>
       </c>
       <c r="G71">
-        <v>-9.566334169246268</v>
+        <v>-9.325114422750357</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.21757643405717</v>
       </c>
       <c r="E72">
-        <v>-19.51017803959068</v>
+        <v>-18.07973730151588</v>
       </c>
       <c r="F72">
-        <v>-2.190104984528467</v>
+        <v>-2.478987347478558</v>
       </c>
       <c r="G72">
-        <v>-9.126190044002774</v>
+        <v>-9.143530609576949</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.352185746949738</v>
       </c>
       <c r="E73">
-        <v>-18.62319746300367</v>
+        <v>-18.43970443346142</v>
       </c>
       <c r="F73">
-        <v>-2.179877132206102</v>
+        <v>-2.489129049591033</v>
       </c>
       <c r="G73">
-        <v>-9.475012934193716</v>
+        <v>-9.097933955293156</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.477895527385455</v>
       </c>
       <c r="E74">
-        <v>-19.38597625492168</v>
+        <v>-18.41217694880046</v>
       </c>
       <c r="F74">
-        <v>-2.832344858858146</v>
+        <v>-2.604860259436152</v>
       </c>
       <c r="G74">
-        <v>-8.437594409745985</v>
+        <v>-9.039273135075431</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.593211162647622</v>
       </c>
       <c r="E75">
-        <v>-19.79326092349099</v>
+        <v>-18.77565354431547</v>
       </c>
       <c r="F75">
-        <v>-2.700232683622668</v>
+        <v>-2.756527703949519</v>
       </c>
       <c r="G75">
-        <v>-8.531467647636351</v>
+        <v>-8.836300796839328</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.695145328465473</v>
       </c>
       <c r="E76">
-        <v>-19.31909293974664</v>
+        <v>-18.81896323201079</v>
       </c>
       <c r="F76">
-        <v>-2.370819132020999</v>
+        <v>-2.843121918768568</v>
       </c>
       <c r="G76">
-        <v>-8.274656534442309</v>
+        <v>-8.180116251308915</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.785520585313583</v>
       </c>
       <c r="E77">
-        <v>-20.82403813577753</v>
+        <v>-19.12197737705895</v>
       </c>
       <c r="F77">
-        <v>-2.790479998688062</v>
+        <v>-3.150214282334401</v>
       </c>
       <c r="G77">
-        <v>-7.889152682746227</v>
+        <v>-7.996513027194283</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.863341575610384</v>
       </c>
       <c r="E78">
-        <v>-19.01269392746874</v>
+        <v>-18.97013597102322</v>
       </c>
       <c r="F78">
-        <v>-2.915228816080057</v>
+        <v>-2.812442503638485</v>
       </c>
       <c r="G78">
-        <v>-7.57193024508612</v>
+        <v>-8.200164159024075</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.930516058938066</v>
       </c>
       <c r="E79">
-        <v>-20.77384242370566</v>
+        <v>-19.75093554687966</v>
       </c>
       <c r="F79">
-        <v>-2.599230674566726</v>
+        <v>-3.021502555287414</v>
       </c>
       <c r="G79">
-        <v>-8.091775181207121</v>
+        <v>-7.785768502310436</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.990523197103374</v>
       </c>
       <c r="E80">
-        <v>-21.4624739338415</v>
+        <v>-20.47750664246782</v>
       </c>
       <c r="F80">
-        <v>-3.103200290388515</v>
+        <v>-3.051091010548009</v>
       </c>
       <c r="G80">
-        <v>-7.91088843683954</v>
+        <v>-7.297564485261434</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.044355259798764</v>
       </c>
       <c r="E81">
-        <v>-22.17101593906858</v>
+        <v>-21.11919440499913</v>
       </c>
       <c r="F81">
-        <v>-2.987789658728279</v>
+        <v>-3.193720138329431</v>
       </c>
       <c r="G81">
-        <v>-7.213558556553181</v>
+        <v>-7.144279838083399</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.099484664127695</v>
       </c>
       <c r="E82">
-        <v>-22.69172480891896</v>
+        <v>-21.95259440228452</v>
       </c>
       <c r="F82">
-        <v>-2.963210341152413</v>
+        <v>-2.905271839898407</v>
       </c>
       <c r="G82">
-        <v>-7.507491847088262</v>
+        <v>-7.588056814425427</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.159035892302714</v>
       </c>
       <c r="E83">
-        <v>-24.07528825077041</v>
+        <v>-21.60786540268978</v>
       </c>
       <c r="F83">
-        <v>-2.946842629640497</v>
+        <v>-3.192986204810551</v>
       </c>
       <c r="G83">
-        <v>-6.69533880894015</v>
+        <v>-6.854787424097803</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.227361659665003</v>
       </c>
       <c r="E84">
-        <v>-23.82510710698539</v>
+        <v>-23.27079875751715</v>
       </c>
       <c r="F84">
-        <v>-3.121906483078533</v>
+        <v>-3.212197701616277</v>
       </c>
       <c r="G84">
-        <v>-7.168990535638287</v>
+        <v>-6.8188296388444</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.31059853021565</v>
       </c>
       <c r="E85">
-        <v>-24.90917832699214</v>
+        <v>-23.97252118974886</v>
       </c>
       <c r="F85">
-        <v>-2.878149434395945</v>
+        <v>-3.23115406126194</v>
       </c>
       <c r="G85">
-        <v>-6.759539629180217</v>
+        <v>-6.585684925368801</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.409501207105435</v>
       </c>
       <c r="E86">
-        <v>-25.50668838066125</v>
+        <v>-24.65886843365605</v>
       </c>
       <c r="F86">
-        <v>-2.630311019519764</v>
+        <v>-3.409589370029371</v>
       </c>
       <c r="G86">
-        <v>-6.401838902007194</v>
+        <v>-6.859802664457331</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.529309925082192</v>
       </c>
       <c r="E87">
-        <v>-26.75547180859937</v>
+        <v>-25.75552388397702</v>
       </c>
       <c r="F87">
-        <v>-2.85130701707563</v>
+        <v>-3.237643491495472</v>
       </c>
       <c r="G87">
-        <v>-7.117227302630283</v>
+        <v>-6.129110079041136</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.672262720810322</v>
       </c>
       <c r="E88">
-        <v>-27.20704216952533</v>
+        <v>-26.24414088992045</v>
       </c>
       <c r="F88">
-        <v>-3.208903284455343</v>
+        <v>-3.088556411441825</v>
       </c>
       <c r="G88">
-        <v>-6.269602077722715</v>
+        <v>-6.018176930620141</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.838595496706962</v>
       </c>
       <c r="E89">
-        <v>-28.6082899851979</v>
+        <v>-27.76198596032626</v>
       </c>
       <c r="F89">
-        <v>-3.073871942492398</v>
+        <v>-3.189800303779384</v>
       </c>
       <c r="G89">
-        <v>-7.102426991543262</v>
+        <v>-6.5019870645223</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.036741162088624</v>
       </c>
       <c r="E90">
-        <v>-30.25532692367949</v>
+        <v>-28.9395958057908</v>
       </c>
       <c r="F90">
-        <v>-2.77755746720439</v>
+        <v>-3.199444157082775</v>
       </c>
       <c r="G90">
-        <v>-6.599412220428874</v>
+        <v>-6.147179042356231</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.268744995705302</v>
       </c>
       <c r="E91">
-        <v>-30.90086471310892</v>
+        <v>-30.50578425601762</v>
       </c>
       <c r="F91">
-        <v>-3.263980604700079</v>
+        <v>-3.251649527542006</v>
       </c>
       <c r="G91">
-        <v>-6.47682470815315</v>
+        <v>-6.184883415741089</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.541353068350169</v>
       </c>
       <c r="E92">
-        <v>-33.4084241954327</v>
+        <v>-31.94019546411895</v>
       </c>
       <c r="F92">
-        <v>-3.042687223246608</v>
+        <v>-3.547983055280278</v>
       </c>
       <c r="G92">
-        <v>-6.277413425539327</v>
+        <v>-6.205986064271058</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.863234968315544</v>
       </c>
       <c r="E93">
-        <v>-34.7754765456623</v>
+        <v>-33.50827362549857</v>
       </c>
       <c r="F93">
-        <v>-3.091312389790939</v>
+        <v>-3.587529315089927</v>
       </c>
       <c r="G93">
-        <v>-7.141428904989904</v>
+        <v>-6.278120937323518</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.232152438184674</v>
       </c>
       <c r="E94">
-        <v>-35.64647971828269</v>
+        <v>-34.85993625116402</v>
       </c>
       <c r="F94">
-        <v>-3.379614895559071</v>
+        <v>-3.49581661808898</v>
       </c>
       <c r="G94">
-        <v>-6.365463397619213</v>
+        <v>-6.696560637408791</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.65639688568541</v>
       </c>
       <c r="E95">
-        <v>-36.59877784937528</v>
+        <v>-36.69715911923782</v>
       </c>
       <c r="F95">
-        <v>-2.614186848024271</v>
+        <v>-3.531957459505719</v>
       </c>
       <c r="G95">
-        <v>-6.51774551887426</v>
+        <v>-6.207978062394077</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.136633737890818</v>
       </c>
       <c r="E96">
-        <v>-38.97271398713968</v>
+        <v>-38.39703528879954</v>
       </c>
       <c r="F96">
-        <v>-3.135894295042206</v>
+        <v>-3.517427066893213</v>
       </c>
       <c r="G96">
-        <v>-6.583554557782453</v>
+        <v>-6.62259563239796</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.661872292280511</v>
       </c>
       <c r="E97">
-        <v>-40.20709615480897</v>
+        <v>-40.56936831903978</v>
       </c>
       <c r="F97">
-        <v>-3.453949272816687</v>
+        <v>-3.644164794419329</v>
       </c>
       <c r="G97">
-        <v>-6.20671707275657</v>
+        <v>-6.965932042830677</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.24132510773854</v>
       </c>
       <c r="E98">
-        <v>-42.38203947836686</v>
+        <v>-41.59928373997643</v>
       </c>
       <c r="F98">
-        <v>-3.004433216585327</v>
+        <v>-3.656425460348165</v>
       </c>
       <c r="G98">
-        <v>-6.552392710342924</v>
+        <v>-7.410440027658217</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.841771768963655</v>
       </c>
       <c r="E99">
-        <v>-45.2639631996937</v>
+        <v>-43.56077899731175</v>
       </c>
       <c r="F99">
-        <v>-3.402173825039509</v>
+        <v>-3.750805500386126</v>
       </c>
       <c r="G99">
-        <v>-7.622675287703589</v>
+        <v>-7.188422307629943</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.482913443192722</v>
       </c>
       <c r="E100">
-        <v>-46.0938931889172</v>
+        <v>-45.42142805386325</v>
       </c>
       <c r="F100">
-        <v>-3.175401621583922</v>
+        <v>-3.589959745049741</v>
       </c>
       <c r="G100">
-        <v>-7.877134120021037</v>
+        <v>-7.949891655658477</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.10279354675427</v>
       </c>
       <c r="E101">
-        <v>-48.2553250777326</v>
+        <v>-47.58353068630761</v>
       </c>
       <c r="F101">
-        <v>-3.157620715282831</v>
+        <v>-3.871900389164372</v>
       </c>
       <c r="G101">
-        <v>-7.982174817899889</v>
+        <v>-8.327393575182798</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.75613120354285</v>
       </c>
       <c r="E102">
-        <v>-48.40882465338977</v>
+        <v>-49.73251436247967</v>
       </c>
       <c r="F102">
-        <v>-3.874856832424963</v>
+        <v>-3.847181905864835</v>
       </c>
       <c r="G102">
-        <v>-7.934228493484093</v>
+        <v>-8.19839668493589</v>
       </c>
     </row>
   </sheetData>
